--- a/reconciliacao-fonte-primaria/test/fixtures/fechamento-ficticio-teste.xlsx
+++ b/reconciliacao-fonte-primaria/test/fixtures/fechamento-ficticio-teste.xlsx
@@ -1,52 +1,178 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="FOPAG TESTE" sheetId="1" r:id="rId1"/>
-    <sheet name="BALANCETE 02.2026" sheetId="2" r:id="rId2"/>
-    <sheet name="Balancete 03-2026" sheetId="3" r:id="rId3"/>
-    <sheet name="BALANCETE 04.2026" sheetId="4" r:id="rId4"/>
-    <sheet name="RAZÃO 04.2026" sheetId="5" r:id="rId5"/>
-    <sheet name="CHECK" sheetId="6" r:id="rId6"/>
+    <sheet sheetId="1" name="FOPAG TESTE" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="BALANCETE 02.2026" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="Balancete 03-2026" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="BALANCETE 04.2026" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="RAZÃO 04.2026" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="CHECK" state="visible" r:id="rId9"/>
   </sheets>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="48">
+  <si>
+    <t>planilha de teste — dados 100% fictícios</t>
+  </si>
+  <si>
+    <t>NOME</t>
+  </si>
+  <si>
+    <t>MES</t>
+  </si>
+  <si>
+    <t>Centro  de   Custo</t>
+  </si>
+  <si>
+    <t>SALARIO</t>
+  </si>
+  <si>
+    <t>HORAS EXTRAS</t>
+  </si>
+  <si>
+    <t>BENEFICIOS</t>
+  </si>
+  <si>
+    <t>ENCARGOS</t>
+  </si>
+  <si>
+    <t>TOTAL PROVENTOS</t>
+  </si>
+  <si>
+    <t>ANA TESTE SILVA</t>
+  </si>
+  <si>
+    <t>Comercial</t>
+  </si>
+  <si>
+    <t>BRUNO TESTE COSTA</t>
+  </si>
+  <si>
+    <t>Operações</t>
+  </si>
+  <si>
+    <t>CARLA TESTE LIMA</t>
+  </si>
+  <si>
+    <t>Código</t>
+  </si>
+  <si>
+    <t>Classificação</t>
+  </si>
+  <si>
+    <t>Nome</t>
+  </si>
+  <si>
+    <t>Débito</t>
+  </si>
+  <si>
+    <t>Crédito</t>
+  </si>
+  <si>
+    <t>4.2.01.001.001</t>
+  </si>
+  <si>
+    <t>SALARIO BASE TESTE</t>
+  </si>
+  <si>
+    <t>4.2.01.001.002</t>
+  </si>
+  <si>
+    <t>HORAS EXTRAS TESTE</t>
+  </si>
+  <si>
+    <t>4.2.01.001.003</t>
+  </si>
+  <si>
+    <t>BENEFICIOS TESTE</t>
+  </si>
+  <si>
+    <t>4.2.01.004.001</t>
+  </si>
+  <si>
+    <t>ENCARGOS TESTE</t>
+  </si>
+  <si>
+    <t>4.2.01.001</t>
+  </si>
+  <si>
+    <t>GRUPO SALARIAL TESTE (pai)</t>
+  </si>
+  <si>
+    <t>4.2.01.001.009</t>
+  </si>
+  <si>
+    <t>AUXILIO CRECHE TESTE (fantasma)</t>
+  </si>
+  <si>
+    <t>Data</t>
+  </si>
+  <si>
+    <t>Histórico</t>
+  </si>
+  <si>
+    <t>Contra</t>
+  </si>
+  <si>
+    <t>Reclassificação teste 1</t>
+  </si>
+  <si>
+    <t>Reclassificação teste 2</t>
+  </si>
+  <si>
+    <t>JANEIRO</t>
+  </si>
+  <si>
+    <t>FEVEREIRO</t>
+  </si>
+  <si>
+    <t>MARÇO</t>
+  </si>
+  <si>
+    <t>ABRIL</t>
+  </si>
+  <si>
+    <t>FOPAG</t>
+  </si>
+  <si>
+    <t>CONTABIL</t>
+  </si>
+  <si>
+    <t>DIFERENÇA</t>
+  </si>
+  <si>
+    <t>DESCRIÇÃO CONTA</t>
+  </si>
+  <si>
+    <t>SALARIO BASE TESTE (4.2.01.001.001)</t>
+  </si>
+  <si>
+    <t>HORAS EXTRAS TESTE (4.2.01.001.002)</t>
+  </si>
+  <si>
+    <t>BENEFICIOS TESTE (4.2.01.001.003)</t>
+  </si>
+  <si>
+    <t>ENCARGOS TESTE (4.2.01.004.001)</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -70,14 +196,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -402,49 +536,50 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H14"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>planilha de teste — dados 100% fictícios</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>NOME</v>
-      </c>
-      <c r="B2" t="str">
-        <v>MES</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Centro  de   Custo</v>
-      </c>
-      <c r="D2" t="str">
-        <v>SALARIO</v>
-      </c>
-      <c r="E2" t="str">
-        <v>HORAS EXTRAS</v>
-      </c>
-      <c r="F2" t="str">
-        <v>BENEFICIOS</v>
-      </c>
-      <c r="G2" t="str">
-        <v>ENCARGOS</v>
-      </c>
-      <c r="H2" t="str">
-        <v>TOTAL PROVENTOS</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>ANA TESTE SILVA</v>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>9</v>
       </c>
       <c r="B3" s="1">
         <v>46023</v>
       </c>
-      <c r="C3" t="str">
-        <v>Comercial</v>
+      <c r="C3" t="s">
+        <v>10</v>
       </c>
       <c r="D3">
         <v>8000</v>
@@ -462,15 +597,15 @@
         <v>10800</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>BRUNO TESTE COSTA</v>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>11</v>
       </c>
       <c r="B4" s="1">
         <v>46023</v>
       </c>
-      <c r="C4" t="str">
-        <v>Operações</v>
+      <c r="C4" t="s">
+        <v>12</v>
       </c>
       <c r="D4">
         <v>6500</v>
@@ -488,15 +623,15 @@
         <v>8700</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>CARLA TESTE LIMA</v>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>13</v>
       </c>
       <c r="B5" s="1">
         <v>46023</v>
       </c>
-      <c r="C5" t="str">
-        <v>Comercial</v>
+      <c r="C5" t="s">
+        <v>10</v>
       </c>
       <c r="D5">
         <v>9200</v>
@@ -514,15 +649,15 @@
         <v>12000</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>ANA TESTE SILVA</v>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>9</v>
       </c>
       <c r="B6" s="1">
         <v>46054</v>
       </c>
-      <c r="C6" t="str">
-        <v>Comercial</v>
+      <c r="C6" t="s">
+        <v>10</v>
       </c>
       <c r="D6">
         <v>8080</v>
@@ -540,15 +675,15 @@
         <v>10902</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>BRUNO TESTE COSTA</v>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>11</v>
       </c>
       <c r="B7" s="1">
         <v>46054</v>
       </c>
-      <c r="C7" t="str">
-        <v>Operações</v>
+      <c r="C7" t="s">
+        <v>12</v>
       </c>
       <c r="D7">
         <v>6565</v>
@@ -566,15 +701,15 @@
         <v>8782</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>CARLA TESTE LIMA</v>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>13</v>
       </c>
       <c r="B8" s="1">
         <v>46054</v>
       </c>
-      <c r="C8" t="str">
-        <v>Comercial</v>
+      <c r="C8" t="s">
+        <v>10</v>
       </c>
       <c r="D8">
         <v>9292</v>
@@ -592,15 +727,15 @@
         <v>12113</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>ANA TESTE SILVA</v>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>9</v>
       </c>
       <c r="B9" s="1">
         <v>46082</v>
       </c>
-      <c r="C9" t="str">
-        <v>Comercial</v>
+      <c r="C9" t="s">
+        <v>10</v>
       </c>
       <c r="D9">
         <v>8160</v>
@@ -618,15 +753,15 @@
         <v>11004</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>BRUNO TESTE COSTA</v>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>11</v>
       </c>
       <c r="B10" s="1">
         <v>46082</v>
       </c>
-      <c r="C10" t="str">
-        <v>Operações</v>
+      <c r="C10" t="s">
+        <v>12</v>
       </c>
       <c r="D10">
         <v>6630</v>
@@ -644,15 +779,15 @@
         <v>8864</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>CARLA TESTE LIMA</v>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>13</v>
       </c>
       <c r="B11" s="1">
         <v>46082</v>
       </c>
-      <c r="C11" t="str">
-        <v>Comercial</v>
+      <c r="C11" t="s">
+        <v>10</v>
       </c>
       <c r="D11">
         <v>9384</v>
@@ -670,15 +805,15 @@
         <v>12226</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>ANA TESTE SILVA</v>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>9</v>
       </c>
       <c r="B12" s="1">
         <v>46113</v>
       </c>
-      <c r="C12" t="str">
-        <v>Comercial</v>
+      <c r="C12" t="s">
+        <v>10</v>
       </c>
       <c r="D12">
         <v>8240</v>
@@ -696,15 +831,15 @@
         <v>11106</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>BRUNO TESTE COSTA</v>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>11</v>
       </c>
       <c r="B13" s="1">
         <v>46113</v>
       </c>
-      <c r="C13" t="str">
-        <v>Operações</v>
+      <c r="C13" t="s">
+        <v>12</v>
       </c>
       <c r="D13">
         <v>6695</v>
@@ -722,15 +857,15 @@
         <v>8946</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>CARLA TESTE LIMA</v>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>13</v>
       </c>
       <c r="B14" s="1">
         <v>46113</v>
       </c>
-      <c r="C14" t="str">
-        <v>Comercial</v>
+      <c r="C14" t="s">
+        <v>10</v>
       </c>
       <c r="D14">
         <v>9476</v>
@@ -749,42 +884,42 @@
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H15"/>
-  </ignoredErrors>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Código</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Classificação</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Nome</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Débito</v>
-      </c>
-      <c r="I1" t="str">
-        <v>Crédito</v>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2</v>
       </c>
-      <c r="B2" t="str">
-        <v>4.2.01.001.001</v>
-      </c>
-      <c r="E2" t="str">
-        <v>SALARIO BASE TESTE</v>
+      <c r="B2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" t="s">
+        <v>20</v>
       </c>
       <c r="H2">
         <v>23937</v>
@@ -793,15 +928,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>3</v>
       </c>
-      <c r="B3" t="str">
-        <v>4.2.01.001.002</v>
-      </c>
-      <c r="E3" t="str">
-        <v>HORAS EXTRAS TESTE</v>
+      <c r="B3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" t="s">
+        <v>22</v>
       </c>
       <c r="H3">
         <v>656.5</v>
@@ -810,15 +945,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>4</v>
       </c>
-      <c r="B4" t="str">
-        <v>4.2.01.001.003</v>
-      </c>
-      <c r="E4" t="str">
-        <v>BENEFICIOS TESTE</v>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" t="s">
+        <v>24</v>
       </c>
       <c r="H4">
         <v>1800</v>
@@ -827,15 +962,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>5</v>
       </c>
-      <c r="B5" t="str">
-        <v>4.2.01.004.001</v>
-      </c>
-      <c r="E5" t="str">
-        <v>ENCARGOS TESTE</v>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" t="s">
+        <v>26</v>
       </c>
       <c r="H5">
         <v>5654.25</v>
@@ -845,42 +980,42 @@
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I6"/>
-  </ignoredErrors>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Código</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Classificação</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Nome</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Débito</v>
-      </c>
-      <c r="I1" t="str">
-        <v>Crédito</v>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2</v>
       </c>
-      <c r="B2" t="str">
-        <v>4.2.01.001.001</v>
-      </c>
-      <c r="E2" t="str">
-        <v>SALARIO BASE TESTE</v>
+      <c r="B2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" t="s">
+        <v>20</v>
       </c>
       <c r="H2">
         <v>24174</v>
@@ -889,15 +1024,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>3</v>
       </c>
-      <c r="B3" t="str">
-        <v>4.2.01.001.002</v>
-      </c>
-      <c r="E3" t="str">
-        <v>HORAS EXTRAS TESTE</v>
+      <c r="B3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" t="s">
+        <v>22</v>
       </c>
       <c r="H3">
         <v>663</v>
@@ -906,15 +1041,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>4</v>
       </c>
-      <c r="B4" t="str">
-        <v>4.2.01.001.003</v>
-      </c>
-      <c r="E4" t="str">
-        <v>BENEFICIOS TESTE</v>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" t="s">
+        <v>24</v>
       </c>
       <c r="H4">
         <v>1800</v>
@@ -923,15 +1058,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>5</v>
       </c>
-      <c r="B5" t="str">
-        <v>4.2.01.004.001</v>
-      </c>
-      <c r="E5" t="str">
-        <v>ENCARGOS TESTE</v>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" t="s">
+        <v>26</v>
       </c>
       <c r="H5">
         <v>5457</v>
@@ -941,42 +1076,42 @@
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I6"/>
-  </ignoredErrors>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I7"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Código</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Classificação</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Nome</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Débito</v>
-      </c>
-      <c r="I1" t="str">
-        <v>Crédito</v>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2</v>
       </c>
-      <c r="B2" t="str">
-        <v>4.2.01.001</v>
-      </c>
-      <c r="E2" t="str">
-        <v>GRUPO SALARIAL TESTE (pai)</v>
+      <c r="B2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" t="s">
+        <v>28</v>
       </c>
       <c r="H2">
         <v>24751.2</v>
@@ -985,15 +1120,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>3</v>
       </c>
-      <c r="B3" t="str">
-        <v>4.2.01.001.001</v>
-      </c>
-      <c r="E3" t="str">
-        <v>SALARIO BASE TESTE</v>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" t="s">
+        <v>20</v>
       </c>
       <c r="H3">
         <v>24411</v>
@@ -1002,15 +1137,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>4</v>
       </c>
-      <c r="B4" t="str">
-        <v>4.2.01.001.002</v>
-      </c>
-      <c r="E4" t="str">
-        <v>HORAS EXTRAS TESTE</v>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" t="s">
+        <v>22</v>
       </c>
       <c r="H4">
         <v>669.5</v>
@@ -1019,15 +1154,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>5</v>
       </c>
-      <c r="B5" t="str">
-        <v>4.2.01.001.003</v>
-      </c>
-      <c r="E5" t="str">
-        <v>BENEFICIOS TESTE</v>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" t="s">
+        <v>24</v>
       </c>
       <c r="H5">
         <v>1800</v>
@@ -1036,15 +1171,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>6</v>
       </c>
-      <c r="B6" t="str">
-        <v>4.2.01.001.009</v>
-      </c>
-      <c r="E6" t="str">
-        <v>AUXILIO CRECHE TESTE (fantasma)</v>
+      <c r="B6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" t="s">
+        <v>30</v>
       </c>
       <c r="H6">
         <v>340.2</v>
@@ -1053,15 +1188,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>7</v>
       </c>
-      <c r="B7" t="str">
-        <v>4.2.01.004.001</v>
-      </c>
-      <c r="E7" t="str">
-        <v>ENCARGOS TESTE</v>
+      <c r="B7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" t="s">
+        <v>26</v>
       </c>
       <c r="H7">
         <v>5510.5</v>
@@ -1071,39 +1206,39 @@
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I8"/>
-  </ignoredErrors>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H12"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Data</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Histórico</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Contra</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Débito</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Crédito</v>
-      </c>
-    </row>
-    <row r="10">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>46124</v>
       </c>
-      <c r="B10" t="str">
-        <v>Reclassificação teste 1</v>
+      <c r="B10" t="s">
+        <v>34</v>
       </c>
       <c r="F10">
         <v>180.4</v>
@@ -1112,12 +1247,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>46132</v>
       </c>
-      <c r="B11" t="str">
-        <v>Reclassificação teste 2</v>
+      <c r="B11" t="s">
+        <v>35</v>
       </c>
       <c r="F11">
         <v>95.1</v>
@@ -1127,31 +1262,31 @@
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H12"/>
-  </ignoredErrors>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:Q8"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1">
-      <c r="C1" t="str">
-        <v>JANEIRO</v>
-      </c>
-      <c r="G1" t="str">
-        <v>FEVEREIRO</v>
-      </c>
-      <c r="K1" t="str">
-        <v>MARÇO</v>
-      </c>
-      <c r="O1" t="str">
-        <v>ABRIL</v>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="3:15" x14ac:dyDescent="0.25">
+      <c r="C1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K1" t="s">
+        <v>38</v>
+      </c>
+      <c r="O1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C2" s="1">
         <v>46023</v>
       </c>
@@ -1165,52 +1300,52 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="3">
-      <c r="C3" t="str">
-        <v>FOPAG</v>
-      </c>
-      <c r="D3" t="str">
-        <v>CONTABIL</v>
-      </c>
-      <c r="E3" t="str">
-        <v>DIFERENÇA</v>
-      </c>
-      <c r="G3" t="str">
-        <v>FOPAG</v>
-      </c>
-      <c r="H3" t="str">
-        <v>CONTABIL</v>
-      </c>
-      <c r="I3" t="str">
-        <v>DIFERENÇA</v>
-      </c>
-      <c r="K3" t="str">
-        <v>FOPAG</v>
-      </c>
-      <c r="L3" t="str">
-        <v>CONTABIL</v>
-      </c>
-      <c r="M3" t="str">
-        <v>DIFERENÇA</v>
-      </c>
-      <c r="O3" t="str">
-        <v>FOPAG</v>
-      </c>
-      <c r="P3" t="str">
-        <v>CONTABIL</v>
-      </c>
-      <c r="Q3" t="str">
-        <v>DIFERENÇA</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>DESCRIÇÃO CONTA</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>SALARIO BASE TESTE (4.2.01.001.001)</v>
+    <row r="3" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="C3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H3" t="s">
+        <v>41</v>
+      </c>
+      <c r="I3" t="s">
+        <v>42</v>
+      </c>
+      <c r="K3" t="s">
+        <v>40</v>
+      </c>
+      <c r="L3" t="s">
+        <v>41</v>
+      </c>
+      <c r="M3" t="s">
+        <v>42</v>
+      </c>
+      <c r="O3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P3" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>44</v>
       </c>
       <c r="C5">
         <f>SUMIFS('FOPAG TESTE'!$D$3:$D$100,'FOPAG TESTE'!$B$3:$B$100,C2)</f>
@@ -1231,7 +1366,7 @@
         <v>23937</v>
       </c>
       <c r="I5">
-        <f>=G5-H5</f>
+        <f>G5-H5</f>
         <v>0</v>
       </c>
       <c r="K5">
@@ -1243,7 +1378,7 @@
         <v>0</v>
       </c>
       <c r="M5">
-        <f>=K5-L5</f>
+        <f>K5-L5</f>
         <v>24174</v>
       </c>
       <c r="O5">
@@ -1255,13 +1390,13 @@
         <v>24411</v>
       </c>
       <c r="Q5">
-        <f>=O5-P5</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>HORAS EXTRAS TESTE (4.2.01.001.002)</v>
+        <f>O5-P5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>45</v>
       </c>
       <c r="C6">
         <f>SUMIFS('FOPAG TESTE'!$E$3:$E$100,'FOPAG TESTE'!$B$3:$B$100,C2)</f>
@@ -1282,7 +1417,7 @@
         <v>656.5</v>
       </c>
       <c r="I6">
-        <f>=G6-H6</f>
+        <f>G6-H6</f>
         <v>0</v>
       </c>
       <c r="K6">
@@ -1294,7 +1429,7 @@
         <v>0</v>
       </c>
       <c r="M6">
-        <f>=K6-L6</f>
+        <f>K6-L6</f>
         <v>663</v>
       </c>
       <c r="O6">
@@ -1306,13 +1441,13 @@
         <v>669.5</v>
       </c>
       <c r="Q6">
-        <f>=O6-P6</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>BENEFICIOS TESTE (4.2.01.001.003)</v>
+        <f>O6-P6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>46</v>
       </c>
       <c r="C7">
         <f>SUMIFS('FOPAG TESTE'!$F$3:$F$100,'FOPAG TESTE'!$B$3:$B$100,C2)</f>
@@ -1333,7 +1468,7 @@
         <v>1800</v>
       </c>
       <c r="I7">
-        <f>=G7-H7</f>
+        <f>G7-H7</f>
         <v>0</v>
       </c>
       <c r="K7">
@@ -1345,7 +1480,7 @@
         <v>0</v>
       </c>
       <c r="M7">
-        <f>=K7-L7</f>
+        <f>K7-L7</f>
         <v>1800</v>
       </c>
       <c r="O7">
@@ -1357,13 +1492,13 @@
         <v>1800</v>
       </c>
       <c r="Q7">
-        <f>=O7-P7</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>ENCARGOS TESTE (4.2.01.004.001)</v>
+        <f>O7-P7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>47</v>
       </c>
       <c r="C8">
         <f>SUMIFS('FOPAG TESTE'!$G$3:$G$100,'FOPAG TESTE'!$B$3:$B$100,C2)</f>
@@ -1384,7 +1519,7 @@
         <v>5654.25</v>
       </c>
       <c r="I8">
-        <f>=G8-H8</f>
+        <f>G8-H8</f>
         <v>-250.75</v>
       </c>
       <c r="K8">
@@ -1396,7 +1531,7 @@
         <v>0</v>
       </c>
       <c r="M8">
-        <f>=K8-L8</f>
+        <f>K8-L8</f>
         <v>5457</v>
       </c>
       <c r="O8">
@@ -1408,13 +1543,12 @@
         <v>5786</v>
       </c>
       <c r="Q8">
-        <f>=O8-P8</f>
+        <f>O8-P8</f>
         <v>-275.5</v>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T9"/>
-  </ignoredErrors>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
--- a/reconciliacao-fonte-primaria/test/fixtures/fechamento-ficticio-teste.xlsx
+++ b/reconciliacao-fonte-primaria/test/fixtures/fechamento-ficticio-teste.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="48">
   <si>
     <t>planilha de teste — dados 100% fictícios</t>
   </si>
@@ -987,91 +987,76 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" t="s">
         <v>15</v>
       </c>
+      <c r="C1" t="s">
+        <v>16</v>
+      </c>
       <c r="E1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H1" t="s">
         <v>17</v>
       </c>
-      <c r="I1" t="s">
+      <c r="F1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>19</v>
       </c>
-      <c r="E2" t="s">
+      <c r="C2" t="s">
         <v>20</v>
       </c>
-      <c r="H2">
+      <c r="E2">
         <v>24174</v>
       </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="F2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>21</v>
       </c>
-      <c r="E3" t="s">
+      <c r="C3" t="s">
         <v>22</v>
       </c>
-      <c r="H3">
+      <c r="E3">
         <v>663</v>
       </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>4</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="F3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>23</v>
       </c>
-      <c r="E4" t="s">
+      <c r="C4" t="s">
         <v>24</v>
       </c>
-      <c r="H4">
+      <c r="E4">
         <v>1800</v>
       </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>5</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="F4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>25</v>
       </c>
-      <c r="E5" t="s">
+      <c r="C5" t="s">
         <v>26</v>
       </c>
-      <c r="H5">
+      <c r="E5">
         <v>5457</v>
       </c>
-      <c r="I5">
+      <c r="F5">
         <v>0</v>
       </c>
     </row>
